--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,10 +1511,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119657228</v>
+        <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99142</v>
+        <v>99355</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1522,54 +1522,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>219811</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Svanamyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504838</v>
+        <v>504887</v>
       </c>
       <c r="R8" t="n">
-        <v>7007557</v>
+        <v>7007444</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1596,17 +1584,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1619,40 +1602,34 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
-        </is>
-      </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119657228</t>
+          <t>https://artportalen.se/Sighting/136949734</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119656913</v>
+        <v>119657228</v>
       </c>
       <c r="B9" t="n">
-        <v>97983</v>
+        <v>99142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1660,26 +1637,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1692,10 +1681,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>504831</v>
+        <v>504838</v>
       </c>
       <c r="R9" t="n">
-        <v>7007540</v>
+        <v>7007557</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1732,7 +1721,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Minst ett skott av tvåblad. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1769,16 +1758,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119656913</t>
+          <t>https://artportalen.se/Sighting/119657228</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119657801</v>
+        <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>97983</v>
+        <v>99377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1786,42 +1775,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granskog vid Åsens vägskäl, Jmt</t>
+          <t>Svanamyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>504852</v>
+        <v>504885</v>
       </c>
       <c r="R10" t="n">
-        <v>7007539</v>
+        <v>7007442</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1848,12 +1837,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1866,40 +1855,34 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Sara Lundkvist</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119657801</t>
+          <t>https://artportalen.se/Sighting/136949733</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119657304</v>
+        <v>119656913</v>
       </c>
       <c r="B11" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1907,38 +1890,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
@@ -1951,10 +1922,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>504838</v>
+        <v>504831</v>
       </c>
       <c r="R11" t="n">
-        <v>7007557</v>
+        <v>7007540</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1991,7 +1962,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+          <t>Måttlig förekomst av revlummer. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2028,16 +1999,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119657304</t>
+          <t>https://artportalen.se/Sighting/119656913</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119657398</v>
+        <v>119657801</v>
       </c>
       <c r="B12" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2045,38 +2016,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
@@ -2127,11 +2086,6 @@
           <t>2024-09-05</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2165,6 +2119,282 @@
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657801</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>119657304</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>504838</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7007557</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Minst 4 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119657304</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>119657398</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granskog vid Åsens vägskäl, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>504852</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7007539</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-09-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Minst 2 st skott av spindelblomster. Obs! Denna fyndplats ligger inom en avverkningsanmälan med beteckning A 7710-2024.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Något äldre flerskiktad granskog med bitvis större mängder död ved, mestadels liggande död ved men även stående död ved i form av gran med toppbrott. Dominans av gran med inblandning av björk, sälg och rönn. På frisk-fuktig och frisk mark.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119657398</t>
         </is>
@@ -2183,6 +2413,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 7710-2024 artfynd.xlsx
+++ b/artfynd/A 7710-2024 artfynd.xlsx
@@ -1514,7 +1514,7 @@
         <v>136949734</v>
       </c>
       <c r="B8" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1767,7 +1767,7 @@
         <v>136949733</v>
       </c>
       <c r="B10" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
